--- a/Result/profitability/5016.xlsx
+++ b/Result/profitability/5016.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>0.44875</v>
+        <v>0.47</v>
       </c>
       <c r="N2" t="n">
-        <v>10.14375</v>
+        <v>10.57125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0.69375</v>
+        <v>0.7375</v>
       </c>
       <c r="N3" t="n">
-        <v>11.6475</v>
+        <v>12.0775</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.97</v>
+        <v>1.0125</v>
       </c>
       <c r="N4" t="n">
-        <v>13.3275</v>
+        <v>13.78</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6925</v>
+        <v>0.7575</v>
       </c>
       <c r="N5" t="n">
-        <v>11.39625</v>
+        <v>11.92</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.45875</v>
+        <v>0.51375</v>
       </c>
       <c r="N6" t="n">
-        <v>8.815000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0.215</v>
+        <v>0.245</v>
       </c>
       <c r="N7" t="n">
-        <v>6.492500000000001</v>
+        <v>6.84</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.89</v>
       </c>
       <c r="M8" t="n">
-        <v>0.26125</v>
+        <v>0.31125</v>
       </c>
       <c r="N8" t="n">
-        <v>6.536250000000001</v>
+        <v>6.8775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.32625</v>
       </c>
       <c r="N10" t="n">
-        <v>7.523750000000001</v>
+        <v>7.52375</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>0.17625</v>
+        <v>0.1762500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>6.891249999999999</v>
@@ -1899,7 +1899,7 @@
         <v>1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02625000000000002</v>
+        <v>0.02625000000000005</v>
       </c>
       <c r="N12" t="n">
         <v>5.85375</v>
@@ -2026,7 +2026,7 @@
         <v>0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.26875</v>
+        <v>0.2687500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>8.08625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>618</v>
+      </c>
+      <c r="D75" t="n">
+        <v>536</v>
+      </c>
+      <c r="E75" t="n">
+        <v>82</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>49</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>47</v>
+      </c>
+      <c r="K75" t="n">
+        <v>38</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.3225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.729999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2587677725118482</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4609460946094608</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
